--- a/InputData/trans/FoVObE/Fraction of Veh Owned by Entity.xlsx
+++ b/InputData/trans/FoVObE/Fraction of Veh Owned by Entity.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shigu\Documents\_swj\_Talanoa\CPSA Fletcher\dados\InputData (BR) 2024\d17 trans\FoVObE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saido\OneDrive\Documents\eps-brazil-cpl\InputData\trans\FoVObE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E10E6C3-C124-4D23-921B-056A2CB5706A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4656" yWindow="1356" windowWidth="17628" windowHeight="12000" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4650" yWindow="1350" windowWidth="17625" windowHeight="12000" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -30,7 +29,7 @@
     <definedName name="outputfrac_nonenergy">#REF!</definedName>
     <definedName name="outputfrac_other">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -429,7 +428,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -879,14 +878,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="8">
-    <cellStyle name="Data_Sheet1 (2)_1" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Hed Side" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Hiperlink" xfId="7" builtinId="8"/>
+    <cellStyle name="Data_Sheet1 (2)_1" xfId="4"/>
+    <cellStyle name="Hed Side" xfId="3"/>
+    <cellStyle name="Lien hypertexte" xfId="7" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentagem" xfId="6" builtinId="5"/>
-    <cellStyle name="Source Text" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Table Title" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Title-1" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Pourcentage" xfId="6" builtinId="5"/>
+    <cellStyle name="Source Text" xfId="5"/>
+    <cellStyle name="Table Title" xfId="1"/>
+    <cellStyle name="Title-1" xfId="2"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
@@ -994,7 +993,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4219AC8A-C851-4E18-886B-062BE1ECA0CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4219AC8A-C851-4E18-886B-062BE1ECA0CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1038,7 +1037,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D4FC022-F918-416D-89F4-2F128FAA58A4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1D4FC022-F918-416D-89F4-2F128FAA58A4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1087,7 +1086,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{741F48AD-560B-4D77-AAFB-838566CD06BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{741F48AD-560B-4D77-AAFB-838566CD06BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1117,9 +1116,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1157,9 +1156,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1194,7 +1193,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1229,7 +1228,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1402,23 +1401,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" customWidth="1"/>
-    <col min="2" max="2" width="100.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="100.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
@@ -1426,101 +1425,101 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="34">
         <v>2017</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="36" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="35" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="34">
         <v>2017</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" s="36" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>119</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" xr:uid="{F0502F94-9ED2-4B1A-ABA7-3A9524076815}"/>
-    <hyperlink ref="B17" r:id="rId2" xr:uid="{7A915761-EF2B-4BD8-B2B2-65D40FD453E5}"/>
+    <hyperlink ref="B8" r:id="rId1"/>
+    <hyperlink ref="B17" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
@@ -1528,18 +1527,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="58.33203125" customWidth="1"/>
-    <col min="3" max="4" width="16.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" customWidth="1"/>
-    <col min="6" max="6" width="78.44140625" customWidth="1"/>
+    <col min="2" max="2" width="58.28515625" customWidth="1"/>
+    <col min="3" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="78.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>1</v>
       </c>
@@ -1559,7 +1558,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
@@ -1579,7 +1578,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>9</v>
       </c>
@@ -1600,7 +1599,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>11</v>
       </c>
@@ -1620,7 +1619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>13</v>
       </c>
@@ -1640,7 +1639,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>15</v>
       </c>
@@ -1660,7 +1659,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
         <v>22</v>
       </c>
@@ -1681,7 +1680,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
         <v>3</v>
       </c>
@@ -1701,7 +1700,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>10</v>
       </c>
@@ -1721,7 +1720,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>12</v>
       </c>
@@ -1741,7 +1740,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>14</v>
       </c>
@@ -1761,7 +1760,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
         <v>16</v>
       </c>
@@ -1781,7 +1780,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
         <v>23</v>
       </c>
@@ -1793,7 +1792,7 @@
       <c r="E13" s="27"/>
       <c r="F13" s="27"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>20</v>
       </c>
@@ -1805,34 +1804,34 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5F21F3-A7E8-4714-BE33-2DF8847F3A9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F48"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.5546875" customWidth="1"/>
-    <col min="2" max="2" width="54.6640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.109375" customWidth="1"/>
-    <col min="6" max="6" width="47.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="47.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -1840,7 +1839,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -1848,7 +1847,7 @@
         <v>2.2020786406437756E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -1856,7 +1855,7 @@
         <v>9.0092391802747019E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -1872,7 +1871,7 @@
         <v>1.8017523713989358E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
         <v>87</v>
       </c>
@@ -1880,10 +1879,10 @@
         <v>4.904754930070182E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>39</v>
       </c>
@@ -1891,7 +1890,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -1899,7 +1898,7 @@
         <v>3.9315618317814327E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>65</v>
       </c>
@@ -1907,7 +1906,7 @@
         <v>9.2243548220630578E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>59</v>
       </c>
@@ -1915,7 +1914,7 @@
         <v>2.5591170948187771E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
         <v>87</v>
       </c>
@@ -1924,7 +1923,7 @@
         <v>0.15715033748663268</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
         <v>99</v>
       </c>
@@ -1932,7 +1931,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
         <v>98</v>
       </c>
@@ -1940,7 +1939,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>52</v>
       </c>
@@ -1951,7 +1950,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>53</v>
       </c>
@@ -1962,7 +1961,7 @@
         <v>2.3117122504209692E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>53</v>
       </c>
@@ -1973,7 +1972,7 @@
         <v>1.7507071829735373E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>53</v>
       </c>
@@ -1984,7 +1983,7 @@
         <v>3.2795253012077023E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>53</v>
       </c>
@@ -1995,7 +1994,7 @@
         <v>2.3757774218404481E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>53</v>
       </c>
@@ -2006,7 +2005,7 @@
         <v>2.5591170948187771E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>53</v>
       </c>
@@ -2017,7 +2016,7 @@
         <v>3.9315618317814327E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>53</v>
       </c>
@@ -2028,7 +2027,7 @@
         <v>2.2020786406437756E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>53</v>
       </c>
@@ -2039,7 +2038,7 @@
         <v>1.8017523713989358E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>53</v>
       </c>
@@ -2050,7 +2049,7 @@
         <v>3.4205700503589336E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>53</v>
       </c>
@@ -2061,7 +2060,7 @@
         <v>3.5090520131377118E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>53</v>
       </c>
@@ -2072,7 +2071,7 @@
         <v>9.2243548220630578E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>53</v>
       </c>
@@ -2083,7 +2082,7 @@
         <v>6.2744062559738425E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>53</v>
       </c>
@@ -2094,7 +2093,7 @@
         <v>8.4593754353820341E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>53</v>
       </c>
@@ -2105,7 +2104,7 @@
         <v>1.3091291937331022E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>53</v>
       </c>
@@ -2116,7 +2115,7 @@
         <v>3.0357499478468873E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>53</v>
       </c>
@@ -2127,7 +2126,7 @@
         <v>2.4968163140259625E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>53</v>
       </c>
@@ -2138,7 +2137,7 @@
         <v>2.3110369499157818E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="63" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>53</v>
       </c>
@@ -2149,7 +2148,7 @@
         <v>0.11987236446263898</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>53</v>
       </c>
@@ -2160,7 +2159,7 @@
         <v>5.8138044010715446E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>53</v>
       </c>
@@ -2171,7 +2170,7 @@
         <v>9.0092391802747019E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>53</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>6.3329301796566734E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>53</v>
       </c>
@@ -2193,7 +2192,7 @@
         <v>2.0275875627793455E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>53</v>
       </c>
@@ -2204,7 +2203,7 @@
         <v>3.3134121352104595E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>53</v>
       </c>
@@ -2215,7 +2214,7 @@
         <v>1.2554555162046196E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>53</v>
       </c>
@@ -2226,7 +2225,7 @@
         <v>7.1336422553775879E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="296.39999999999998" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="299.25" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>53</v>
       </c>
@@ -2237,7 +2236,7 @@
         <v>0.18349232373441351</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>53</v>
       </c>
@@ -2295,45 +2294,45 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A394B04-9F48-4D7C-99E6-96493902E462}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J10" s="37" t="s">
         <v>112</v>
       </c>
@@ -2341,7 +2340,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J11" t="s">
         <v>106</v>
       </c>
@@ -2349,7 +2348,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J12" t="s">
         <v>107</v>
       </c>
@@ -2357,7 +2356,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J13" t="s">
         <v>108</v>
       </c>
@@ -2365,7 +2364,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J14" t="s">
         <v>109</v>
       </c>
@@ -2373,7 +2372,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J15" t="s">
         <v>110</v>
       </c>
@@ -2381,7 +2380,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J16" t="s">
         <v>111</v>
       </c>
@@ -2396,22 +2395,22 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD0E761E-DD35-4A50-BF7C-9B648E01761F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="10" width="21.109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="21.44140625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="10" width="21.140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>41</v>
       </c>
@@ -2447,7 +2446,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -2456,7 +2455,7 @@
         <v>2.560717709316894E-3</v>
       </c>
       <c r="C2" s="43">
-        <f>SUM(G2:L2)</f>
+        <f t="shared" ref="C2:C7" si="0">SUM(G2:L2)</f>
         <v>9.9640174100549227E-4</v>
       </c>
       <c r="D2" s="40">
@@ -2487,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -2496,7 +2495,7 @@
         <v>0.6</v>
       </c>
       <c r="C3" s="43">
-        <f>SUM(G3:L3)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="D3" s="40">
@@ -2527,7 +2526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -2536,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="43">
-        <f>SUM(G4:L4)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D4" s="40">
@@ -2567,7 +2566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -2576,7 +2575,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="43">
-        <f>SUM(G5:L5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D5" s="40">
@@ -2607,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -2616,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="43">
-        <f>SUM(G6:L6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D6" s="40">
@@ -2647,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -2656,7 +2655,7 @@
         <v>0.01</v>
       </c>
       <c r="C7" s="43">
-        <f>SUM(G7:L7)</f>
+        <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
       <c r="D7" s="40">
@@ -2694,19 +2693,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535F7217-8465-4E8A-9CE6-CFC73EA6457C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="8" width="21.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="8" width="21.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>41</v>
       </c>
@@ -2738,7 +2737,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -2773,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -2810,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -2845,7 +2844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -2880,7 +2879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -2916,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -2957,25 +2956,25 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="10" width="21.109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="21.44140625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="10" width="21.140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>41</v>
       </c>
@@ -2999,7 +2998,7 @@
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -3012,8 +3011,8 @@
         <v>9.9640174100549227E-4</v>
       </c>
       <c r="D2" s="40">
-        <f>Results!E2</f>
-        <v>0.99644288054967767</v>
+        <f>1-C2</f>
+        <v>0.99900359825899454</v>
       </c>
       <c r="E2" s="40">
         <v>0</v>
@@ -3026,7 +3025,7 @@
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -3053,7 +3052,7 @@
       <c r="K3" s="40"/>
       <c r="L3" s="40"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -3080,7 +3079,7 @@
       <c r="K4" s="40"/>
       <c r="L4" s="40"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -3107,7 +3106,7 @@
       <c r="K5" s="40"/>
       <c r="L5" s="40"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -3134,7 +3133,7 @@
       <c r="K6" s="40"/>
       <c r="L6" s="40"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -3147,7 +3146,7 @@
         <v>0.01</v>
       </c>
       <c r="D7" s="40">
-        <f>Results!E7</f>
+        <f>1-C7-B7</f>
         <v>0.98</v>
       </c>
       <c r="E7" s="40">
@@ -3168,22 +3167,22 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="8" width="21.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="8" width="21.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>41</v>
       </c>
@@ -3205,7 +3204,7 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -3230,13 +3229,13 @@
       <c r="I2" s="40"/>
       <c r="J2" s="40"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="40">
-        <f>Results!C9</f>
-        <v>0</v>
+        <f>1-C3</f>
+        <v>0.20619788678733453</v>
       </c>
       <c r="C3" s="40">
         <f>Results!$D9-SUM(Set_frght!F3:J3)</f>
@@ -3255,7 +3254,7 @@
       <c r="I3" s="40"/>
       <c r="J3" s="40"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -3280,7 +3279,7 @@
       <c r="I4" s="40"/>
       <c r="J4" s="40"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -3305,7 +3304,7 @@
       <c r="I5" s="40"/>
       <c r="J5" s="40"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -3322,7 +3321,8 @@
         <v>0</v>
       </c>
       <c r="E6" s="40">
-        <v>0</v>
+        <f>1-C6</f>
+        <v>0.54</v>
       </c>
       <c r="F6" s="40"/>
       <c r="G6" s="40"/>
@@ -3330,7 +3330,7 @@
       <c r="I6" s="40"/>
       <c r="J6" s="40"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
